--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct+DICE/adaptive/std/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct+DICE/adaptive/std/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -688,6 +688,228 @@
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>dice_p=10,ash_p=None,react_th=1.0,scale_th=0.1,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>88.15000000000001</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>97.91</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>94.41</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=1.0,scale_th=0.1,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>48.23</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>88.33</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>94.55</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=1.0,scale_th=0.01,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>88.29000000000001</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>94.66</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=1.1,scale_th=0.01,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>88.19</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>94.66</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>93.17</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=1.2,scale_th=0.01,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>92.63</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>88.31999999999999</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>97.70999999999999</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=1.1,scale_th=0.05,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>88.29000000000001</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>94.66</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=1.1,scale_th=0.01,type=std</t>
         </is>
       </c>
     </row>
